--- a/master/result/39_霸道总裁：独家宠爱/39_霸道总裁_契约娇妻的逆袭.xlsx
+++ b/master/result/39_霸道总裁：独家宠爱/39_霸道总裁_契约娇妻的逆袭.xlsx
@@ -397,588 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>outskirts</v>
       </c>
       <c r="B2" t="str">
-        <v>outskirts</v>
+        <v>/outskirts/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>郊区</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>mission</v>
       </c>
       <c r="B3" t="str">
-        <v>mission</v>
+        <v>/mission/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>使命</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>attendant</v>
       </c>
       <c r="B4" t="str">
-        <v>attendant</v>
+        <v>/attendant/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>服务员</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>slam</v>
       </c>
       <c r="B5" t="str">
-        <v>slam</v>
+        <v>/slam/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>砰地关上</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dirty</v>
       </c>
       <c r="B6" t="str">
-        <v>dirty</v>
+        <v>/dirty/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>弄脏的</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>chief</v>
       </c>
       <c r="B7" t="str">
-        <v>chief</v>
+        <v>/tʃiːf/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>主要的</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>monument</v>
       </c>
       <c r="B8" t="str">
-        <v>monument</v>
+        <v>/monument/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>纪念碑</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>drum</v>
       </c>
       <c r="B9" t="str">
-        <v>drum</v>
+        <v>/drum/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>鼓</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>expect</v>
       </c>
       <c r="B10" t="str">
-        <v>expect</v>
+        <v>/ɪkˈspekt/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>预期</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>fog</v>
       </c>
       <c r="B11" t="str">
-        <v>fog</v>
+        <v>/fog/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>雾</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>texture</v>
       </c>
       <c r="B12" t="str">
-        <v>texture</v>
+        <v>/texture/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>质地</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>patience</v>
       </c>
       <c r="B13" t="str">
-        <v>patience</v>
+        <v>/patience/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>耐心</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>excursion</v>
       </c>
       <c r="B14" t="str">
-        <v>excursion</v>
+        <v>/excursion/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>短途旅行</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>distinct</v>
       </c>
       <c r="B15" t="str">
-        <v>distinct</v>
+        <v>/distinct/</v>
       </c>
       <c r="C15" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>清楚的</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>plane</v>
       </c>
       <c r="B16" t="str">
-        <v>plane</v>
+        <v>/plane/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>飞机</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>zone</v>
       </c>
       <c r="B17" t="str">
-        <v>zone</v>
+        <v>/zone/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>地区</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>complement</v>
       </c>
       <c r="B18" t="str">
-        <v>complement</v>
+        <v>/complement/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>补足</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>discuss</v>
       </c>
       <c r="B19" t="str">
-        <v>discuss</v>
+        <v>/dɪˈskʌs/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>讨论</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>disrupt</v>
       </c>
       <c r="B20" t="str">
-        <v>disrupt</v>
+        <v>/disrupt/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>使混乱</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>preside</v>
       </c>
       <c r="B21" t="str">
-        <v>preside</v>
+        <v>/preside/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>主持</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>trifle</v>
       </c>
       <c r="B22" t="str">
-        <v>trifle</v>
+        <v>/trifle/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>小事</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>fracture</v>
       </c>
       <c r="B23" t="str">
-        <v>fracture</v>
+        <v>/fracture/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>裂缝</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>maximum</v>
       </c>
       <c r="B24" t="str">
-        <v>maximum</v>
+        <v>/maximum/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>最大值</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>cargo</v>
       </c>
       <c r="B25" t="str">
-        <v>cargo</v>
+        <v>/ˈkɑːɡəʊ/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>货物</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>restless</v>
       </c>
       <c r="B26" t="str">
-        <v>restless</v>
+        <v>/restless/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>不平静的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>endurance</v>
       </c>
       <c r="B27" t="str">
-        <v>endurance</v>
+        <v>/endurance/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>忍耐</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>convey</v>
       </c>
       <c r="B28" t="str">
-        <v>convey</v>
+        <v>/kənˈveɪ/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>传达</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>electronic</v>
       </c>
       <c r="B29" t="str">
-        <v>electronic</v>
+        <v>/electronic/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>电子的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>ruler</v>
       </c>
       <c r="B30" t="str">
-        <v>ruler</v>
+        <v>/ruler/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>统治者</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>success</v>
       </c>
       <c r="B31" t="str">
-        <v>success</v>
+        <v>/success/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>成功</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>traffic</v>
       </c>
       <c r="B32" t="str">
-        <v>traffic</v>
+        <v>/traffic/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>交通</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>cooperative</v>
       </c>
       <c r="B33" t="str">
-        <v>cooperative</v>
+        <v>/cooperative/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>合作的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>ghost</v>
       </c>
       <c r="B34" t="str">
-        <v>ghost</v>
+        <v>/ghost/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>鬼魂</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>puff</v>
       </c>
       <c r="B35" t="str">
-        <v>puff</v>
+        <v>/puff/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>一阵</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>distress</v>
       </c>
       <c r="B36" t="str">
-        <v>distress</v>
+        <v>/distress/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>苦恼</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>calorie</v>
       </c>
       <c r="B37" t="str">
-        <v>calorie</v>
+        <v>/calorie/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>卡路里</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>pant</v>
       </c>
       <c r="B38" t="str">
-        <v>pant</v>
+        <v>/pant/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>喘气</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>soil</v>
       </c>
       <c r="B39" t="str">
-        <v>soil</v>
+        <v>/soil/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>泥土</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>organic</v>
       </c>
       <c r="B40" t="str">
-        <v>organic</v>
+        <v>/organic/</v>
       </c>
       <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>有机的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>breadth</v>
       </c>
       <c r="B41" t="str">
-        <v>breadth</v>
+        <v>/breadth/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>宽度</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>oblige</v>
       </c>
       <c r="B42" t="str">
-        <v>oblige</v>
+        <v>/oblige/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>强迫</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>synthesis</v>
       </c>
       <c r="B43" t="str">
-        <v>synthesis</v>
+        <v>/synthesis/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>综合</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>assumption</v>
       </c>
       <c r="B44" t="str">
-        <v>assumption</v>
+        <v>/əˈsʌmpʃn/</v>
       </c>
       <c r="C44" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>假定</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>simulate</v>
       </c>
       <c r="B45" t="str">
-        <v>simulate</v>
+        <v>/simulate/</v>
       </c>
       <c r="C45" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D45" t="str">
         <v>模拟</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>wake</v>
       </c>
       <c r="B46" t="str">
-        <v>wake</v>
+        <v>/weɪk/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>醒来</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>nourish</v>
       </c>
       <c r="B47" t="str">
-        <v>nourish</v>
+        <v>/nourish/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>养育</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>spouse</v>
       </c>
       <c r="B48" t="str">
-        <v>spouse</v>
+        <v>/spouse/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>配偶</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>up</v>
       </c>
       <c r="B49" t="str">
-        <v>up</v>
+        <v>/up/</v>
       </c>
       <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>向上</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>prayer</v>
       </c>
       <c r="B50" t="str">
-        <v>prayer</v>
+        <v>/prayer/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>祈祷</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>whenever</v>
       </c>
       <c r="B51" t="str">
-        <v>whenever</v>
+        <v>/whenever/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>无论何时</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>permission</v>
       </c>
       <c r="B52" t="str">
-        <v>permission</v>
+        <v>/permission/</v>
       </c>
       <c r="C52" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D52" t="str">
         <v>允许</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>